--- a/data/trans_orig/CLASESOCIAL_Hogar_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CLASESOCIAL_Hogar_R2-Clase-trans_orig.xlsx
@@ -4123,7 +4123,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>599812</t>
+          <t>603883</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>697472</t>
+          <t>695898</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1758722</t>
+          <t>1756835</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1874330</t>
+          <t>1872386</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2386371</t>
+          <t>2389734</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2546137</t>
+          <t>2548391</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1177587</t>
+          <t>1182260</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1295040</t>
+          <t>1291882</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>669763</t>
+          <t>668407</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>761631</t>
+          <t>764210</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1877946</t>
+          <t>1884986</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2030559</t>
+          <t>2031048</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>502803</t>
+          <t>499735</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>587079</t>
+          <t>586623</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>142595</t>
+          <t>146100</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>194139</t>
+          <t>193396</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>664154</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>763155</t>
+          <t>763618</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>332112</t>
+          <t>329431</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>405521</t>
+          <t>403656</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>338076</t>
+          <t>335875</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>412182</t>
+          <t>408246</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>689070</t>
+          <t>689287</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>795843</t>
+          <t>790287</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>435160</t>
+          <t>432486</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>516845</t>
+          <t>515032</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>278822</t>
+          <t>273465</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>342619</t>
+          <t>340539</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>730490</t>
+          <t>736393</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>841847</t>
+          <t>841043</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9131,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>730082</t>
+          <t>727225</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>831846</t>
+          <t>826414</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1802337</t>
+          <t>1816965</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1927299</t>
+          <t>1934178</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2566804</t>
+          <t>2565143</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2737270</t>
+          <t>2735389</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1098547</t>
+          <t>1102393</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1213518</t>
+          <t>1211433</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>717585</t>
+          <t>714189</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>818227</t>
+          <t>813292</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1851860</t>
+          <t>1849598</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2013927</t>
+          <t>2013237</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>583397</t>
+          <t>585274</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>675684</t>
+          <t>676652</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>231269</t>
+          <t>232308</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>292526</t>
+          <t>296691</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>831079</t>
+          <t>830943</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>953851</t>
+          <t>945163</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>379269</t>
+          <t>380428</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>461909</t>
+          <t>465860</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>301749</t>
+          <t>300467</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>374524</t>
+          <t>375063</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>702236</t>
+          <t>701835</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>812977</t>
+          <t>812347</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>397051</t>
+          <t>399381</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>480075</t>
+          <t>480162</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>280093</t>
+          <t>279966</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>353175</t>
+          <t>355128</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>699548</t>
+          <t>699730</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>808753</t>
+          <t>811759</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14841,12 +14841,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>852444</t>
+          <t>854347</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>961037</t>
+          <t>958562</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1758303</t>
+          <t>1758090</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1875817</t>
+          <t>1883523</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2642453</t>
+          <t>2657679</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2803331</t>
+          <t>2820917</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1099546</t>
+          <t>1093665</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1207276</t>
+          <t>1208147</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>775947</t>
+          <t>770458</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>877477</t>
+          <t>881597</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1899822</t>
+          <t>1899860</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2053917</t>
+          <t>2049061</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>479151</t>
+          <t>480099</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>565326</t>
+          <t>564909</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>140483</t>
+          <t>142216</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>194903</t>
+          <t>195283</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>638827</t>
+          <t>637212</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>737815</t>
+          <t>742649</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>341358</t>
+          <t>339123</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>414341</t>
+          <t>416923</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>334751</t>
+          <t>332832</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>407293</t>
+          <t>406402</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15230,47 +15230,47 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>749500</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>693017</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>797334</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t>11,53%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>749500</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>803740</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>391180</t>
+          <t>391509</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>470225</t>
+          <t>473244</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15328,12 +15328,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>312589</t>
+          <t>313787</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>384354</t>
+          <t>385101</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15343,12 +15343,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>718318</t>
+          <t>722601</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>831543</t>
+          <t>828594</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -16204,7 +16204,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -16317,17 +16317,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -16352,17 +16352,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -16387,17 +16387,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -16773,32 +16773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>446441</t>
+          <t>476543</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>439064</t>
+          <t>467219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>449969</t>
+          <t>480539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16808,32 +16808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>366825</t>
+          <t>405202</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>359414</t>
+          <t>395580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>372327</t>
+          <t>411301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16843,32 +16843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>813267</t>
+          <t>881745</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>802316</t>
+          <t>871678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>820544</t>
+          <t>889667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -16886,32 +16886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>15993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16921,32 +16921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16956,32 +16956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>34677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -16999,17 +16999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -17034,17 +17034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -17069,17 +17069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -17342,32 +17342,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>664123</t>
+          <t>467497</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>655559</t>
+          <t>459481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>470296</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -17377,32 +17377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>153659</t>
+          <t>172116</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146435</t>
+          <t>163455</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158757</t>
+          <t>178040</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17412,32 +17412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>817782</t>
+          <t>639613</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>805167</t>
+          <t>628886</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>828819</t>
+          <t>647761</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17455,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -17465,12 +17465,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -17490,32 +17490,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -17525,32 +17525,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -17578,12 +17578,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17603,32 +17603,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -17638,32 +17638,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -17681,17 +17681,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -17716,17 +17716,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -17751,17 +17751,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -17911,32 +17911,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>993593</t>
+          <t>1089586</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>970360</t>
+          <t>1069125</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1008056</t>
+          <t>1104503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17946,32 +17946,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>686417</t>
+          <t>768212</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>412480</t>
+          <t>749096</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>875630</t>
+          <t>782591</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17981,32 +17981,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1680009</t>
+          <t>1857798</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1121800</t>
+          <t>1829142</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1876581</t>
+          <t>1879441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -18024,32 +18024,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27084</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18059,32 +18059,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37372</t>
+          <t>40214</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>52960</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18094,32 +18094,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>52343</t>
+          <t>55430</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35294</t>
+          <t>42203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70147</t>
+          <t>71675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -18137,32 +18137,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>26420</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18172,32 +18172,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>227830</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24583</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>523518</t>
+          <t>35352</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -18207,32 +18207,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>237708</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>24545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>808597</t>
+          <t>53402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -18250,32 +18250,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40883</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18285,32 +18285,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>26475</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>20107</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>41054</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18320,32 +18320,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>42852</t>
+          <t>44597</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65701</t>
+          <t>62628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -18363,17 +18363,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18398,17 +18398,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -18433,17 +18433,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18480,32 +18480,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>436091</t>
+          <t>529425</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>413535</t>
+          <t>511473</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>450015</t>
+          <t>542923</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18515,32 +18515,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>662173</t>
+          <t>628468</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>631776</t>
+          <t>605591</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>707875</t>
+          <t>649107</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18550,32 +18550,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1098263</t>
+          <t>1157893</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1066293</t>
+          <t>1132154</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1142391</t>
+          <t>1184646</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -18593,32 +18593,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>30595</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18628,32 +18628,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>123259</t>
+          <t>141790</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>91710</t>
+          <t>123026</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>148413</t>
+          <t>162881</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18663,32 +18663,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>151217</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119328</t>
+          <t>150253</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>177748</t>
+          <t>196900</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -18706,32 +18706,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18741,32 +18741,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>36833</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23276</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45703</t>
+          <t>48730</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18776,32 +18776,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>44792</t>
+          <t>43801</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32392</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>66707</t>
+          <t>59342</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>977</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -18829,12 +18829,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18854,32 +18854,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18889,32 +18889,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25385</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -18967,32 +18967,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19002,32 +19002,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -19045,17 +19045,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -19080,17 +19080,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -19115,17 +19115,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -19147,7 +19147,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -19162,32 +19162,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>54226</t>
+          <t>51625</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>33557</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>80665</t>
+          <t>73411</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -19197,32 +19197,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>209434</t>
+          <t>236532</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>188318</t>
+          <t>212066</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>233977</t>
+          <t>262449</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19232,32 +19232,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>263660</t>
+          <t>288158</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>236518</t>
+          <t>259568</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>297537</t>
+          <t>324527</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -19275,32 +19275,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>75310</t>
+          <t>71482</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>52671</t>
+          <t>52061</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>102656</t>
+          <t>95858</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -19310,32 +19310,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>269104</t>
+          <t>294219</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>241235</t>
+          <t>269546</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>292674</t>
+          <t>319559</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19345,32 +19345,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>344415</t>
+          <t>365701</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>308329</t>
+          <t>330587</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>380307</t>
+          <t>401334</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -19388,32 +19388,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19423,67 +19423,67 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>120182</t>
+          <t>138117</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>104691</t>
+          <t>118625</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>140783</t>
+          <t>162162</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
+          <t>19,74%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>172239</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>145932</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>200406</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>19,05%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>154434</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>129822</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>181570</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -19501,32 +19501,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>23579</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43433</t>
+          <t>41630</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19536,32 +19536,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>68156</t>
+          <t>74299</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>54718</t>
+          <t>61003</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>86656</t>
+          <t>92197</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19571,32 +19571,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>92679</t>
+          <t>97878</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>74151</t>
+          <t>77772</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>118138</t>
+          <t>123893</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -19614,32 +19614,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>49899</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>72365</t>
+          <t>70922</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19649,32 +19649,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>72192</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>62932</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>91235</t>
+          <t>98579</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19684,32 +19684,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>121208</t>
+          <t>128153</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>103904</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>151360</t>
+          <t>157360</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -19727,17 +19727,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>237326</t>
+          <t>230708</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>237326</t>
+          <t>230708</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>237326</t>
+          <t>230708</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19762,17 +19762,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>739069</t>
+          <t>821421</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>739069</t>
+          <t>821421</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>739069</t>
+          <t>821421</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19797,17 +19797,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>976396</t>
+          <t>1052129</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>976396</t>
+          <t>1052129</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>976396</t>
+          <t>1052129</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19844,32 +19844,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>490316</t>
+          <t>581050</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>386028</t>
+          <t>536193</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>554270</t>
+          <t>635871</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19879,32 +19879,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>871607</t>
+          <t>865000</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>738191</t>
+          <t>821125</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1038982</t>
+          <t>913446</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19914,32 +19914,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1361924</t>
+          <t>1446050</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1185274</t>
+          <t>1378947</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1541680</t>
+          <t>1515796</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -19957,32 +19957,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1096861</t>
+          <t>1191663</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>844410</t>
+          <t>1131681</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1211299</t>
+          <t>1247665</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19992,32 +19992,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1078780</t>
+          <t>1204222</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>858751</t>
+          <t>1152042</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1169012</t>
+          <t>1257972</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20027,32 +20027,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2175641</t>
+          <t>2395885</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1889852</t>
+          <t>2320587</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2335781</t>
+          <t>2486876</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -20070,32 +20070,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>723335</t>
+          <t>523803</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>502066</t>
+          <t>480357</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1391026</t>
+          <t>568105</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20105,32 +20105,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>346016</t>
+          <t>387281</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>284493</t>
+          <t>355084</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>387387</t>
+          <t>420540</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20140,32 +20140,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1069351</t>
+          <t>911083</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>830163</t>
+          <t>856218</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1803644</t>
+          <t>969172</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -20183,32 +20183,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>484633</t>
+          <t>515256</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>364563</t>
+          <t>468890</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>542184</t>
+          <t>558064</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20218,32 +20218,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>683030</t>
+          <t>526208</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>493550</t>
+          <t>485952</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1232838</t>
+          <t>566066</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20253,32 +20253,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1167662</t>
+          <t>1041465</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>951548</t>
+          <t>982666</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1729892</t>
+          <t>1104029</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -20296,32 +20296,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>577734</t>
+          <t>624185</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>439778</t>
+          <t>574070</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>639997</t>
+          <t>675903</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20331,32 +20331,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>576023</t>
+          <t>629822</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>474885</t>
+          <t>586916</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>635499</t>
+          <t>669108</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20366,32 +20366,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1153758</t>
+          <t>1254007</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1011107</t>
+          <t>1194286</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1254649</t>
+          <t>1325087</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -20409,17 +20409,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3372879</t>
+          <t>3435957</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3372879</t>
+          <t>3435957</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3372879</t>
+          <t>3435957</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -20444,17 +20444,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3555456</t>
+          <t>3612533</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3555456</t>
+          <t>3612533</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3555456</t>
+          <t>3612533</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -20479,17 +20479,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6928336</t>
+          <t>7048490</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6928336</t>
+          <t>7048490</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6928336</t>
+          <t>7048490</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
